--- a/02_Source_Code/Tasarim_Optimizasyon_SEO_Performer_1/Data/Config.xlsx
+++ b/02_Source_Code/Tasarim_Optimizasyon_SEO_Performer_1/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/alexandra_veizu_uipath_com/Documents/Documents/Projects/REFrameworkNET5/StudioTemplates/REFramework/contentFiles/any/any/pt2/VisualBasic/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45E19698-36C4-4786-BF89-F5734275DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C26B73A7-0A1C-49D1-AF91-3375A7A62E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Tasarim_Kuyrugu</t>
+    <t>"Buraya Orchestrator kuyruk adınızı yazın."</t>
   </si>
   <si>
     <t>Orchestrator queue Name. The value must match with the queue name defined on Orchestrator.</t>
@@ -63,9 +63,6 @@
     <t>OrchestratorQueueFolder</t>
   </si>
   <si>
-    <t>Tasarim_Projesi</t>
-  </si>
-  <si>
     <t>Folder name. The value must match a folder defined in Orchestrator and queue specified as OrchestratorQueueName should be created in this folder. For classic folders leave the value field empty.</t>
   </si>
   <si>
@@ -163,7 +160,7 @@
     <t>Python_Exe_Path</t>
   </si>
   <si>
-    <t>C:\Users\User\AppData\Local\Programs\Python\Python312\python.exe</t>
+    <t>"Buraya python.exe dosya yolunuzu yazın."</t>
   </si>
   <si>
     <t>Başlangıçta doğrulanacak yerel Python yorumlayıcı dizini.</t>
@@ -181,7 +178,7 @@
     <t>Python_Folder_Path</t>
   </si>
   <si>
-    <t>C:\Users\User\AppData\Local\Programs\Python\Python312</t>
+    <t>"Buraya Python kurulum klasör yolunuzu yazın."</t>
   </si>
   <si>
     <t>Python kurulum klasörü.</t>
@@ -190,7 +187,7 @@
     <t>Python_Library_Path</t>
   </si>
   <si>
-    <t>C:\Users\User\AppData\Local\Programs\Python\Python312\python312.dll</t>
+    <t>"Buraya python312.dll dosya yolunuzu yazın."</t>
   </si>
   <si>
     <t>Python çalışma kütüphanesi (DLL).</t>
@@ -308,6 +305,9 @@
   </si>
   <si>
     <t>Perf_Gemini_Prompt</t>
+  </si>
+  <si>
+    <t>"Buraya Orchestrator klasör adınızı yazın."</t>
   </si>
   <si>
     <t>Gemini'ye gönderilecek tasarım dosyası isimlendirme komutu.</t>
@@ -757,176 +757,176 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="30.75">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
@@ -1962,138 +1962,138 @@
     </row>
     <row r="2" spans="1:26" ht="28.9">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="43.15">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
         <v>64</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>70</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
         <v>76</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" spans="1:3" ht="28.9">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3089,13 +3089,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -3122,13 +3122,13 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
-      </c>
-      <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>89</v>
@@ -3142,7 +3142,7 @@
         <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
         <v>91</v>
@@ -3156,7 +3156,7 @@
         <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
